--- a/Дз 2, Сбор и работа с требованиями и изменениями/Решения/VladimirtsevA_S2T_маппинг.xlsx
+++ b/Дз 2, Сбор и работа с требованиями и изменениями/Решения/VladimirtsevA_S2T_маппинг.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mostov\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project_neoflex\Дз 2, Сбор и работа с требованиями и изменениями\Решения\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA5D899A-07C2-40A2-AD3C-CBBBA7255DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74AF70E1-2157-45E5-85B3-7B50FD2114AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="65">
   <si>
     <t>Source</t>
   </si>
@@ -215,6 +215,18 @@
   </si>
   <si>
     <t>DATE</t>
+  </si>
+  <si>
+    <t>Code_Currency</t>
+  </si>
+  <si>
+    <t>Код валюты</t>
+  </si>
+  <si>
+    <t>CURR_CODE</t>
+  </si>
+  <si>
+    <t>CASE через таблицу currency_dbt</t>
   </si>
 </sst>
 </file>
@@ -617,7 +629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -723,6 +735,12 @@
       <c r="A3" t="s">
         <v>12</v>
       </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
       <c r="D3" t="s">
         <v>15</v>
       </c>
@@ -941,8 +959,11 @@
       <c r="A7" t="s">
         <v>12</v>
       </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
         <v>50</v>
@@ -1041,6 +1062,62 @@
       </c>
       <c r="R8" s="4" t="s">
         <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K9" t="s">
+        <v>19</v>
+      </c>
+      <c r="L9" t="s">
+        <v>20</v>
+      </c>
+      <c r="M9" t="s">
+        <v>63</v>
+      </c>
+      <c r="N9" t="s">
+        <v>62</v>
+      </c>
+      <c r="O9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P9">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>18</v>
+      </c>
+      <c r="R9" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
